--- a/ExcelFiles/Excel Formulas.xlsx
+++ b/ExcelFiles/Excel Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Excel_Github\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8984A1E-6AA7-4B42-A0B9-C5562FC1EC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E2955B-3E39-42CB-A0B4-C6146FD25CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5055" yWindow="960" windowWidth="22500" windowHeight="13725" activeTab="6" xr2:uid="{858A62D9-1599-4210-9775-AAAC6E0CE55F}"/>
+    <workbookView xWindow="5055" yWindow="960" windowWidth="22500" windowHeight="13725" activeTab="7" xr2:uid="{858A62D9-1599-4210-9775-AAAC6E0CE55F}"/>
   </bookViews>
   <sheets>
     <sheet name="Frequency" sheetId="2" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="SUMIFS" sheetId="6" r:id="rId5"/>
     <sheet name="CountA &amp; CountBlank" sheetId="7" r:id="rId6"/>
     <sheet name="Subtotal" sheetId="8" r:id="rId7"/>
+    <sheet name="Rept" sheetId="9" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="Commision_Rate" localSheetId="2">Lookup!$G$11</definedName>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="72">
   <si>
     <t>Emp ID</t>
   </si>
@@ -274,6 +275,30 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Ratings</t>
+  </si>
+  <si>
+    <t>Star</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>Tally</t>
+  </si>
+  <si>
+    <t>Photoshop</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
   </si>
 </sst>
 </file>
@@ -283,7 +308,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,8 +432,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -455,6 +486,12 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -545,7 +582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -624,6 +661,18 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4905,4 +4954,88 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09801BF-F0E0-4212-A13F-6C9B30177D71}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="45">
+        <v>3</v>
+      </c>
+      <c r="C2" s="46" t="str">
+        <f>REPT("*",B2)</f>
+        <v>***</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="45">
+        <v>5</v>
+      </c>
+      <c r="C3" s="46" t="str">
+        <f>REPT("#",B3)</f>
+        <v>#####</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="45">
+        <v>3</v>
+      </c>
+      <c r="C4" s="46" t="str">
+        <f>REPT("@",3)</f>
+        <v>@@@</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="45">
+        <v>2</v>
+      </c>
+      <c r="C5" s="46" t="str">
+        <f>REPT("$",B5)</f>
+        <v>$$</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="45">
+        <v>1</v>
+      </c>
+      <c r="C6" s="46" t="str">
+        <f>REPT("&amp;",B6)</f>
+        <v>&amp;</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>